--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23A.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23A.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>48977</t>
   </si>
@@ -115,34 +115,34 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>655B5032ED2DC8AE9E6BBCC641833289</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>01/01/2023</t>
+  </si>
+  <si>
+    <t>31/12/2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>14/01/2022</t>
+  </si>
+  <si>
+    <t>http://cobatlaxcala.edu.mx/TRANSPARENCIA/TRANSPARENCIA%202023/Depto%20Comunicacion%20Social/</t>
+  </si>
+  <si>
     <t>Departamento de Información y Relaciones Públicas del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>35C3D753999534FC37713448817DE6EE</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>03/04/2022</t>
-  </si>
-  <si>
-    <t>25/07/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 1 de abril de 2022 al 30 de junio de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no tiene autorizado Programa Anual de Trabajo para el Departamento de Información y Relaciones Públicas.</t>
-  </si>
-  <si>
-    <t>837610089AAD732ABD9E4646510A9042</t>
+    <t>19/04/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo 01 de enero de 2023 al 31 de diciembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala , cuenta con un Programa Anual de Comunicación Social o equivalente autorizado, por tal motivo se genera información alguna para la conformación y/o reporte de esta fracción.</t>
   </si>
 </sst>
 </file>
@@ -535,20 +535,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="91.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="90.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="86" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="253.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="248.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
@@ -701,72 +701,37 @@
     </row>
     <row r="8" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="G8" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
